--- a/AAII_Financials/Quarterly/TLGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TLGY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="92">
   <si>
     <t>TLGY</t>
   </si>
@@ -1395,8 +1395,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
+      <c r="D23" s="3">
+        <v>3300</v>
       </c>
       <c r="E23" s="3">
         <v>-800</v>
@@ -1545,8 +1545,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>3300</v>
       </c>
       <c r="E26" s="3">
         <v>-800</v>
@@ -1595,8 +1595,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>3300</v>
       </c>
       <c r="E27" s="3">
         <v>-800</v>
@@ -1895,8 +1895,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>3300</v>
       </c>
       <c r="E33" s="3">
         <v>-800</v>
@@ -1995,8 +1995,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>3300</v>
       </c>
       <c r="E35" s="3">
         <v>-800</v>
@@ -2931,7 +2931,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="E58" s="3">
         <v>900</v>
@@ -3801,7 +3801,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-11600</v>
+        <v>68600</v>
       </c>
       <c r="E76" s="3">
         <v>65200</v>
@@ -3955,8 +3955,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>3300</v>
       </c>
       <c r="E81" s="3">
         <v>-800</v>

--- a/AAII_Financials/Quarterly/TLGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TLGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
   <si>
     <t>TLGY</t>
   </si>
@@ -656,74 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -733,8 +734,14 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -783,8 +790,14 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -833,8 +846,14 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -883,8 +902,14 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -903,8 +928,10 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -953,8 +980,14 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1003,31 +1036,37 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1053,8 +1092,14 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1103,8 +1148,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1120,46 +1171,48 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>400</v>
+      </c>
+      <c r="F17" s="3">
         <v>500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>400</v>
-      </c>
-      <c r="H17" s="3">
-        <v>300</v>
-      </c>
-      <c r="I17" s="3">
-        <v>300</v>
       </c>
       <c r="J17" s="3">
         <v>300</v>
       </c>
       <c r="K17" s="3">
+        <v>300</v>
+      </c>
+      <c r="L17" s="3">
+        <v>300</v>
+      </c>
+      <c r="M17" s="3">
         <v>800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>100</v>
       </c>
-      <c r="M17" s="3">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
+      <c r="O17" s="3">
+        <v>0</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
@@ -1170,8 +1223,14 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1179,37 +1238,37 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-300</v>
       </c>
       <c r="J18" s="3">
         <v>-300</v>
       </c>
       <c r="K18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M18" s="3">
         <v>-800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-100</v>
       </c>
-      <c r="M18" s="3">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
+      <c r="O18" s="3">
+        <v>0</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
@@ -1220,8 +1279,14 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1240,8 +1305,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1249,37 +1316,37 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F20" s="3">
+        <v>3800</v>
+      </c>
+      <c r="G20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>3400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>1500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>2000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>6100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>3000</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1290,8 +1357,14 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1299,29 +1372,29 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F21" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>3000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>1100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>5800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1340,8 +1413,14 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1390,46 +1469,52 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F23" s="3">
         <v>3300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>3000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>5800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-100</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
+      <c r="O23" s="3">
+        <v>0</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
@@ -1440,8 +1525,14 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1490,8 +1581,14 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1540,46 +1637,52 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F26" s="3">
         <v>3300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>3000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>5800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
+      <c r="O26" s="3">
+        <v>0</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
@@ -1590,46 +1693,52 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F27" s="3">
         <v>3300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>3000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>5800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
+      <c r="O27" s="3">
+        <v>0</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
@@ -1640,8 +1749,14 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1690,8 +1805,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1740,8 +1861,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1790,8 +1917,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1840,8 +1973,14 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1849,37 +1988,37 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="G32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-3400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-1500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-2000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-6100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-3000</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -1890,46 +2029,52 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F33" s="3">
         <v>3300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>3000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>5800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
+      <c r="O33" s="3">
+        <v>0</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
@@ -1940,8 +2085,14 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1990,46 +2141,52 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F35" s="3">
         <v>3300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>3000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>5800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
+      <c r="O35" s="3">
+        <v>0</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
@@ -2040,52 +2197,58 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2095,8 +2258,14 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2115,8 +2284,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2135,8 +2306,10 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2144,32 +2317,32 @@
         <v>100</v>
       </c>
       <c r="E41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F41" s="3">
         <v>100</v>
       </c>
       <c r="G41" s="3">
+        <v>100</v>
+      </c>
+      <c r="H41" s="3">
+        <v>100</v>
+      </c>
+      <c r="I41" s="3">
         <v>600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1500</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2185,8 +2358,14 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2235,8 +2414,14 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2285,8 +2470,14 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2335,41 +2526,47 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>300</v>
       </c>
       <c r="H45" s="3">
         <v>300</v>
       </c>
       <c r="I45" s="3">
+        <v>300</v>
+      </c>
+      <c r="J45" s="3">
+        <v>300</v>
+      </c>
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2385,8 +2582,14 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2394,32 +2597,32 @@
         <v>100</v>
       </c>
       <c r="E46" s="3">
+        <v>100</v>
+      </c>
+      <c r="F46" s="3">
+        <v>100</v>
+      </c>
+      <c r="G46" s="3">
         <v>200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1800</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2435,41 +2638,47 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>66000</v>
+      </c>
+      <c r="F47" s="3">
         <v>80100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>78500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>77000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>237500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>236000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>234900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>234600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>234600</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2485,8 +2694,14 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2535,8 +2750,14 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2585,8 +2806,14 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2635,8 +2862,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2685,8 +2918,14 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2699,33 +2938,33 @@
       <c r="F52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2735,8 +2974,14 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2785,47 +3030,53 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>67200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>66000</v>
+      </c>
+      <c r="F54" s="3">
         <v>80300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>78700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>77400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>238400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>237200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>236400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>236400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>236700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>100</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,8 +3086,14 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2855,8 +3112,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2875,41 +3134,43 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>500</v>
+      </c>
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>300</v>
-      </c>
-      <c r="H57" s="3">
-        <v>300</v>
       </c>
       <c r="I57" s="3">
         <v>300</v>
       </c>
       <c r="J57" s="3">
+        <v>300</v>
+      </c>
+      <c r="K57" s="3">
+        <v>300</v>
+      </c>
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,26 +3186,32 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F58" s="3">
         <v>1700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>200</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2954,17 +3221,17 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3">
         <v>100</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
@@ -2975,8 +3242,14 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3005,17 +3278,17 @@
         <v>0</v>
       </c>
       <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3">
         <v>400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>100</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3025,47 +3298,53 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F60" s="3">
         <v>2100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>100</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3075,8 +3354,14 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3125,41 +3410,47 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F62" s="3">
         <v>9600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>12200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>10600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>9100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>11000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>11300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>13100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>19200</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,8 +3466,14 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3225,8 +3522,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3275,8 +3578,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3325,47 +3634,53 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>10800</v>
+      </c>
+      <c r="F66" s="3">
         <v>11700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>13500</v>
-      </c>
-      <c r="F66" s="3">
-        <v>11300</v>
-      </c>
-      <c r="G66" s="3">
-        <v>9500</v>
       </c>
       <c r="H66" s="3">
         <v>11300</v>
       </c>
       <c r="I66" s="3">
+        <v>9500</v>
+      </c>
+      <c r="J66" s="3">
+        <v>11300</v>
+      </c>
+      <c r="K66" s="3">
         <v>11600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>13300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>19400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>100</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3375,8 +3690,14 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3395,8 +3716,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3445,8 +3768,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3495,8 +3824,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3545,8 +3880,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3595,46 +3936,52 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-11600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-13200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-10900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-8600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-10100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-10100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-11500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-17300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-100</v>
       </c>
-      <c r="M72" s="3">
-        <v>0</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
+      <c r="O72" s="3">
+        <v>0</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
@@ -3645,8 +3992,14 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3695,8 +4048,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3745,8 +4104,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3795,46 +4160,52 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>55200</v>
+      </c>
+      <c r="F76" s="3">
         <v>68600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>65200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>66100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>228900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>225900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>224800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>223100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>217300</v>
       </c>
-      <c r="L76" s="3">
-        <v>0</v>
-      </c>
-      <c r="M76" s="3">
-        <v>0</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
+      <c r="N76" s="3">
+        <v>0</v>
+      </c>
+      <c r="O76" s="3">
+        <v>0</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
@@ -3845,8 +4216,14 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3895,52 +4272,58 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3950,46 +4333,52 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F81" s="3">
         <v>3300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>3000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>5800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
+      <c r="O81" s="3">
+        <v>0</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
@@ -4000,8 +4389,14 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4020,8 +4415,10 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4070,8 +4467,14 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4120,8 +4523,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4170,8 +4579,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4220,8 +4635,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4270,8 +4691,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4320,25 +4747,31 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="E89" s="3">
         <v>-200</v>
       </c>
       <c r="F89" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="G89" s="3">
         <v>-200</v>
       </c>
       <c r="H89" s="3">
-        <v>-200</v>
+        <v>-400</v>
       </c>
       <c r="I89" s="3">
         <v>-200</v>
@@ -4347,19 +4780,19 @@
         <v>-200</v>
       </c>
       <c r="K89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M89" s="3">
         <v>-700</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
@@ -4370,8 +4803,14 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4390,8 +4829,10 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4440,8 +4881,14 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4490,8 +4937,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4540,26 +4993,32 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>15100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>162800</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4572,11 +5031,11 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -4590,8 +5049,14 @@
       <c r="R94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4610,8 +5075,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4660,8 +5127,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4710,8 +5183,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4760,8 +5239,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4810,26 +5295,32 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="F100" s="3">
         <v>1100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-162900</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4842,11 +5333,11 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
@@ -4860,8 +5351,14 @@
       <c r="R100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4910,8 +5407,14 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4922,13 +5425,13 @@
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-500</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-200</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-200</v>
       </c>
       <c r="I102" s="3">
         <v>-200</v>
@@ -4937,19 +5440,19 @@
         <v>-200</v>
       </c>
       <c r="K102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M102" s="3">
         <v>1500</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
       </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
@@ -4958,6 +5461,12 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TLGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TLGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
   <si>
     <t>TLGY</t>
   </si>
@@ -656,78 +656,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -740,8 +741,11 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -796,8 +800,11 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -852,8 +859,11 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -908,8 +918,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -930,8 +943,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -986,8 +1000,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1042,16 +1059,19 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+        <v>-600</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1059,17 +1079,17 @@
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1098,8 +1118,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1154,8 +1177,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1173,31 +1199,32 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E17" s="3">
         <v>300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>300</v>
       </c>
       <c r="K17" s="3">
         <v>300</v>
@@ -1206,16 +1233,16 @@
         <v>300</v>
       </c>
       <c r="M17" s="3">
+        <v>300</v>
+      </c>
+      <c r="N17" s="3">
         <v>800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>100</v>
       </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
+      <c r="P17" s="3">
+        <v>0</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
@@ -1229,8 +1256,11 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1238,22 +1268,22 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-300</v>
       </c>
       <c r="K18" s="3">
         <v>-300</v>
@@ -1262,16 +1292,16 @@
         <v>-300</v>
       </c>
       <c r="M18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N18" s="3">
         <v>-800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-100</v>
       </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
+      <c r="P18" s="3">
+        <v>0</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
@@ -1285,8 +1315,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1307,8 +1340,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1316,40 +1350,40 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>600</v>
+      </c>
+      <c r="F20" s="3">
         <v>2300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3800</v>
       </c>
-      <c r="G20" s="3">
-        <v>-600</v>
-      </c>
       <c r="H20" s="3">
-        <v>900</v>
+        <v>-700</v>
       </c>
       <c r="I20" s="3">
+        <v>700</v>
+      </c>
+      <c r="J20" s="3">
         <v>3400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3000</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1363,8 +1397,11 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1372,32 +1409,32 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>300</v>
+      </c>
+      <c r="F21" s="3">
         <v>1900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-800</v>
-      </c>
       <c r="H21" s="3">
-        <v>300</v>
+        <v>-900</v>
       </c>
       <c r="I21" s="3">
+        <v>200</v>
+      </c>
+      <c r="J21" s="3">
         <v>3000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1419,8 +1456,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1475,49 +1515,52 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E23" s="3">
+        <v>300</v>
+      </c>
+      <c r="F23" s="3">
         <v>1900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3300</v>
       </c>
-      <c r="G23" s="3">
-        <v>-800</v>
-      </c>
       <c r="H23" s="3">
-        <v>300</v>
+        <v>-900</v>
       </c>
       <c r="I23" s="3">
+        <v>200</v>
+      </c>
+      <c r="J23" s="3">
         <v>3000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-100</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
+      <c r="P23" s="3">
+        <v>0</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
@@ -1531,8 +1574,11 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1587,8 +1633,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1643,49 +1692,52 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E26" s="3">
+        <v>300</v>
+      </c>
+      <c r="F26" s="3">
         <v>1900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3300</v>
       </c>
-      <c r="G26" s="3">
-        <v>-800</v>
-      </c>
       <c r="H26" s="3">
-        <v>300</v>
+        <v>-900</v>
       </c>
       <c r="I26" s="3">
+        <v>200</v>
+      </c>
+      <c r="J26" s="3">
         <v>3000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-100</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
+      <c r="P26" s="3">
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
@@ -1699,49 +1751,52 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3">
+        <v>300</v>
+      </c>
+      <c r="F27" s="3">
         <v>1900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3300</v>
       </c>
-      <c r="G27" s="3">
-        <v>-800</v>
-      </c>
       <c r="H27" s="3">
-        <v>300</v>
+        <v>-900</v>
       </c>
       <c r="I27" s="3">
+        <v>200</v>
+      </c>
+      <c r="J27" s="3">
         <v>3000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
+      <c r="P27" s="3">
+        <v>0</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
@@ -1755,8 +1810,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1811,8 +1869,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1867,8 +1928,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1923,8 +1987,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1979,8 +2046,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1988,40 +2058,40 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3800</v>
       </c>
-      <c r="G32" s="3">
-        <v>600</v>
-      </c>
       <c r="H32" s="3">
-        <v>-900</v>
+        <v>700</v>
       </c>
       <c r="I32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J32" s="3">
         <v>-3400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3000</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -2035,49 +2105,52 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E33" s="3">
+        <v>300</v>
+      </c>
+      <c r="F33" s="3">
         <v>1900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3300</v>
       </c>
-      <c r="G33" s="3">
-        <v>-800</v>
-      </c>
       <c r="H33" s="3">
-        <v>300</v>
+        <v>-900</v>
       </c>
       <c r="I33" s="3">
+        <v>200</v>
+      </c>
+      <c r="J33" s="3">
         <v>3000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
+      <c r="P33" s="3">
+        <v>0</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
@@ -2091,8 +2164,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2147,49 +2223,52 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3">
+        <v>300</v>
+      </c>
+      <c r="F35" s="3">
         <v>1900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3300</v>
       </c>
-      <c r="G35" s="3">
-        <v>-800</v>
-      </c>
       <c r="H35" s="3">
-        <v>300</v>
+        <v>-900</v>
       </c>
       <c r="I35" s="3">
+        <v>200</v>
+      </c>
+      <c r="J35" s="3">
         <v>3000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
+      <c r="P35" s="3">
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
@@ -2203,55 +2282,58 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2264,8 +2346,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2286,8 +2371,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2308,19 +2394,20 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
         <v>100</v>
       </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
       <c r="F41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G41" s="3">
         <v>100</v>
@@ -2329,23 +2416,23 @@
         <v>100</v>
       </c>
       <c r="I41" s="3">
+        <v>100</v>
+      </c>
+      <c r="J41" s="3">
         <v>600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1500</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2364,8 +2451,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2420,8 +2510,11 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2476,8 +2569,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2532,25 +2628,28 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
       </c>
       <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>300</v>
       </c>
       <c r="I45" s="3">
         <v>300</v>
@@ -2559,17 +2658,17 @@
         <v>300</v>
       </c>
       <c r="K45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L45" s="3">
         <v>400</v>
       </c>
       <c r="M45" s="3">
+        <v>400</v>
+      </c>
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2588,8 +2687,11 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2603,29 +2705,29 @@
         <v>100</v>
       </c>
       <c r="G46" s="3">
+        <v>100</v>
+      </c>
+      <c r="H46" s="3">
         <v>200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1800</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2644,43 +2746,46 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E47" s="3">
         <v>67100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>66000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>80100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>78500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>77000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>237500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>236000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>234900</v>
-      </c>
-      <c r="L47" s="3">
-        <v>234600</v>
       </c>
       <c r="M47" s="3">
         <v>234600</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
+      <c r="N47" s="3">
+        <v>234600</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
@@ -2700,8 +2805,11 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2756,8 +2864,11 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2812,8 +2923,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2868,8 +2982,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2924,8 +3041,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2944,30 +3064,30 @@
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
       </c>
       <c r="L52" s="3">
+        <v>100</v>
+      </c>
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2980,8 +3100,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3036,50 +3159,53 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E54" s="3">
         <v>67200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>66000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>80300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>78700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>77400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>238400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>237200</v>
-      </c>
-      <c r="K54" s="3">
-        <v>236400</v>
       </c>
       <c r="L54" s="3">
         <v>236400</v>
       </c>
       <c r="M54" s="3">
+        <v>236400</v>
+      </c>
+      <c r="N54" s="3">
         <v>236700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>100</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3092,8 +3218,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3114,8 +3243,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3136,28 +3266,29 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
         <v>500</v>
       </c>
       <c r="F57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G57" s="3">
         <v>400</v>
       </c>
       <c r="H57" s="3">
+        <v>400</v>
+      </c>
+      <c r="I57" s="3">
         <v>500</v>
-      </c>
-      <c r="I57" s="3">
-        <v>300</v>
       </c>
       <c r="J57" s="3">
         <v>300</v>
@@ -3166,14 +3297,14 @@
         <v>300</v>
       </c>
       <c r="L57" s="3">
+        <v>300</v>
+      </c>
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3192,29 +3323,32 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1300</v>
+        <v>3500</v>
       </c>
       <c r="E58" s="3">
         <v>1300</v>
       </c>
       <c r="F58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G58" s="3">
         <v>1700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3227,14 +3361,14 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
@@ -3248,8 +3382,11 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3284,14 +3421,14 @@
         <v>0</v>
       </c>
       <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
         <v>400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3304,50 +3441,53 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1800</v>
+        <v>3800</v>
       </c>
       <c r="E60" s="3">
         <v>1800</v>
       </c>
       <c r="F60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G60" s="3">
         <v>2100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>400</v>
-      </c>
-      <c r="J60" s="3">
-        <v>300</v>
       </c>
       <c r="K60" s="3">
         <v>300</v>
       </c>
       <c r="L60" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M60" s="3">
         <v>200</v>
       </c>
       <c r="N60" s="3">
+        <v>200</v>
+      </c>
+      <c r="O60" s="3">
         <v>500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>100</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3360,8 +3500,11 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3416,44 +3559,47 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E62" s="3">
         <v>9300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>19200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,8 +3618,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3528,8 +3677,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3584,8 +3736,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3640,50 +3795,53 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E66" s="3">
         <v>11100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>100</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3696,8 +3854,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3718,8 +3879,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3774,8 +3936,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3830,8 +3995,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3886,8 +4054,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3942,49 +4113,52 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-11000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-10800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-11600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-13200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-10900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-8600</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-10100</v>
       </c>
       <c r="K72" s="3">
         <v>-10100</v>
       </c>
       <c r="L72" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="M72" s="3">
         <v>-11500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-17300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-100</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
+      <c r="P72" s="3">
+        <v>0</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
@@ -3998,8 +4172,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4054,8 +4231,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4110,8 +4290,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4166,49 +4349,52 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E76" s="3">
         <v>56100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>55200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>68600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>65200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>66100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>228900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>225900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>224800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>223100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>217300</v>
       </c>
-      <c r="N76" s="3">
-        <v>0</v>
-      </c>
       <c r="O76" s="3">
         <v>0</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
+      <c r="P76" s="3">
+        <v>0</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
@@ -4222,8 +4408,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4278,55 +4467,58 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4339,49 +4531,52 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E81" s="3">
+        <v>300</v>
+      </c>
+      <c r="F81" s="3">
         <v>1900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3300</v>
       </c>
-      <c r="G81" s="3">
-        <v>-800</v>
-      </c>
       <c r="H81" s="3">
-        <v>300</v>
+        <v>-900</v>
       </c>
       <c r="I81" s="3">
+        <v>200</v>
+      </c>
+      <c r="J81" s="3">
         <v>3000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
+      <c r="P81" s="3">
+        <v>0</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
@@ -4395,8 +4590,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4417,8 +4615,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4473,8 +4672,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4529,8 +4731,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4585,8 +4790,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4641,8 +4849,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4697,8 +4908,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4753,28 +4967,31 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-400</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-200</v>
       </c>
       <c r="J89" s="3">
         <v>-200</v>
@@ -4786,16 +5003,16 @@
         <v>-200</v>
       </c>
       <c r="M89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N89" s="3">
         <v>-700</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
       <c r="O89" s="3">
         <v>0</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
+      <c r="P89" s="3">
+        <v>0</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
@@ -4809,8 +5026,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4831,8 +5051,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4887,8 +5108,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4943,8 +5167,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4999,29 +5226,32 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>15100</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-600</v>
       </c>
       <c r="G94" s="3">
         <v>-600</v>
       </c>
       <c r="H94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I94" s="3">
         <v>162800</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5037,8 +5267,8 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -5055,8 +5285,11 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5077,8 +5310,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5133,8 +5367,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5189,8 +5426,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5245,8 +5485,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5301,29 +5544,32 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-14900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-162900</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5339,8 +5585,8 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P100" s="3">
         <v>0</v>
@@ -5357,8 +5603,11 @@
       <c r="T100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5413,8 +5662,11 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5431,10 +5683,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-500</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-200</v>
       </c>
       <c r="J102" s="3">
         <v>-200</v>
@@ -5446,16 +5698,16 @@
         <v>-200</v>
       </c>
       <c r="M102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N102" s="3">
         <v>1500</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
+      <c r="P102" s="3">
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
@@ -5467,6 +5719,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
